--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N169_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N169_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.54923486683273</v>
+        <v>3.664250665860319</v>
       </c>
       <c r="D2" t="n">
-        <v>11.00504934614612</v>
+        <v>1.788320518748745</v>
       </c>
       <c r="E2" t="n">
-        <v>11.63419597350062</v>
+        <v>1.890556845693851</v>
       </c>
       <c r="F2" t="n">
-        <v>8.108990761669398</v>
+        <v>1.317710998771277</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.12084670934971</v>
+        <v>2.132137590269327</v>
       </c>
       <c r="D3" t="n">
-        <v>14.25185178846159</v>
+        <v>2.315925915625008</v>
       </c>
       <c r="E3" t="n">
-        <v>11.63419597350062</v>
+        <v>1.890556845693851</v>
       </c>
       <c r="F3" t="n">
-        <v>8.108990761669398</v>
+        <v>1.317710998771277</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.34478914696398</v>
+        <v>4.931028236381646</v>
       </c>
       <c r="D4" t="n">
-        <v>19.91230775173988</v>
+        <v>3.23575000965773</v>
       </c>
       <c r="E4" t="n">
-        <v>11.63419597350062</v>
+        <v>1.890556845693851</v>
       </c>
       <c r="F4" t="n">
-        <v>8.108990761669398</v>
+        <v>1.317710998771277</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.82882453369095</v>
+        <v>6.472183986724779</v>
       </c>
       <c r="D5" t="n">
-        <v>19.64508520492248</v>
+        <v>3.192326345799904</v>
       </c>
       <c r="E5" t="n">
-        <v>11.63419597350062</v>
+        <v>1.890556845693851</v>
       </c>
       <c r="F5" t="n">
-        <v>8.108990761669398</v>
+        <v>1.317710998771277</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.72052640645919</v>
+        <v>5.967085541049619</v>
       </c>
       <c r="D6" t="n">
-        <v>5.70087712549569</v>
+        <v>0.9263925328930496</v>
       </c>
       <c r="E6" t="n">
-        <v>11.63419597350062</v>
+        <v>1.890556845693851</v>
       </c>
       <c r="F6" t="n">
-        <v>8.108990761669398</v>
+        <v>1.317710998771277</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.68337985508365</v>
+        <v>2.061049226451094</v>
       </c>
       <c r="D7" t="n">
-        <v>10.91081989155103</v>
+        <v>1.773008232377042</v>
       </c>
       <c r="E7" t="n">
-        <v>11.63419597350062</v>
+        <v>1.890556845693851</v>
       </c>
       <c r="F7" t="n">
-        <v>8.108990761669398</v>
+        <v>1.317710998771277</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.53783737880742</v>
+        <v>7.074898574056206</v>
       </c>
       <c r="D8" t="n">
-        <v>32.5</v>
+        <v>5.28125</v>
       </c>
       <c r="E8" t="n">
-        <v>11.63419597350062</v>
+        <v>1.890556845693851</v>
       </c>
       <c r="F8" t="n">
-        <v>8.108990761669398</v>
+        <v>1.317710998771277</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
